--- a/data/trans_dic/P79_n_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79_n_R2-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,24</t>
+          <t>2,17; 8,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,53</t>
+          <t>3,7; 11,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,8</t>
+          <t>3,45; 8,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,84</t>
+          <t>1,99; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,2</t>
+          <t>1,87; 5,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,2</t>
+          <t>2,21; 4,76</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,25</t>
+          <t>2,63; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,11</t>
+          <t>3,07; 5,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,59</t>
+          <t>3,18; 5,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,94</t>
+          <t>2,81; 6,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,75</t>
+          <t>3,0; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,47</t>
+          <t>3,25; 5,17</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,83</t>
+          <t>3,69; 7,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,98</t>
+          <t>2,72; 5,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,42</t>
+          <t>3,53; 5,69</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,21</t>
+          <t>2,25; 5,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,39</t>
+          <t>2,53; 5,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,95</t>
+          <t>2,69; 4,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,75</t>
+          <t>2,07; 5,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,16</t>
+          <t>1,83; 4,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,31</t>
+          <t>2,34; 4,35</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,52</t>
+          <t>3,47; 5,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,2</t>
+          <t>3,5; 4,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,17</t>
+          <t>3,64; 4,61</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>43163</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6986; 32972</t>
+          <t>8841; 36557</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13340; 42365</t>
+          <t>13405; 41103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24320; 62755</t>
+          <t>26596; 65337</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>33096</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7820; 24742</t>
+          <t>9469; 29345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6517; 21524</t>
+          <t>9374; 25793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17413; 39308</t>
+          <t>21639; 46577</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>51489</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10559; 28141</t>
+          <t>16299; 37192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14155; 30228</t>
+          <t>19131; 36444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28702; 51758</t>
+          <t>39506; 66240</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>60059</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10874; 43884</t>
+          <t>19668; 42374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18100; 33847</t>
+          <t>22106; 40272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31987; 71498</t>
+          <t>46700; 74290</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>54270</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19322; 38342</t>
+          <t>22502; 43875</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14099; 27264</t>
+          <t>16585; 32792</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35365; 60158</t>
+          <t>42965; 69314</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27547</t>
+          <t>30918</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7935; 19173</t>
+          <t>9163; 21716</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6458; 26702</t>
+          <t>11092; 22956</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12913; 38587</t>
+          <t>22746; 40869</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>24882</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6081; 16247</t>
+          <t>6428; 17952</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7786; 17733</t>
+          <t>8497; 19988</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16539; 30573</t>
+          <t>18147; 33703</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>297877</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>98439; 156452</t>
+          <t>122482; 177615</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>102614; 155967</t>
+          <t>130758; 176427</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217030; 298878</t>
+          <t>264928; 335361</t>
         </is>
       </c>
     </row>
